--- a/week-04/Top 10 stores.xlsx
+++ b/week-04/Top 10 stores.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFAE2A6-8B83-4814-B98A-061D630EF2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA35B949-1DD7-40BD-BA01-D60EEC588366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3488243D-BFE5-4F86-A072-067D7AAC313C}"/>
   </bookViews>
   <sheets>
     <sheet name="data-1777485768597" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>name</t>
   </si>
@@ -77,6 +90,9 @@
   </si>
   <si>
     <t>Hy-Vee Wine and Spirits #2</t>
+  </si>
+  <si>
+    <t>Rest of the Stores</t>
   </si>
 </sst>
 </file>
@@ -941,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F591D72-4B95-4F61-BB31-A529D7CDFE0C}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
@@ -1102,6 +1118,11 @@
         <v>868</v>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
